--- a/docs/M Codes.xlsx
+++ b/docs/M Codes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matt\Desktop\ML Desktop\STPtoCNC\v0.95\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matt\Desktop\ML Desktop\STPtoCNC\v0.95\STPtoCNC\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E196B5-5E6B-439C-AA59-F6E0778DB33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757BF37F-143F-4D0D-85F7-6B2C15FF123A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16395" yWindow="1665" windowWidth="21795" windowHeight="17760" xr2:uid="{DE30C894-3D7F-4173-936C-D07AC93A27D4}"/>
+    <workbookView xWindow="13230" yWindow="2415" windowWidth="21795" windowHeight="17760" xr2:uid="{DE30C894-3D7F-4173-936C-D07AC93A27D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="148">
   <si>
     <t>Code</t>
   </si>
@@ -231,6 +231,258 @@
   </si>
   <si>
     <t>We will not need this</t>
+  </si>
+  <si>
+    <t>cut</t>
+  </si>
+  <si>
+    <t>auxiliary</t>
+  </si>
+  <si>
+    <t>clamping</t>
+  </si>
+  <si>
+    <t>pierce</t>
+  </si>
+  <si>
+    <t>scribing</t>
+  </si>
+  <si>
+    <t>safety</t>
+  </si>
+  <si>
+    <t>loading</t>
+  </si>
+  <si>
+    <t>sensing</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>setup</t>
+  </si>
+  <si>
+    <t>material_handling</t>
+  </si>
+  <si>
+    <t>Torch path ready; use only for CAM compatibility mode.</t>
+  </si>
+  <si>
+    <t>Torch currently on; CAM compatibility mode in use.</t>
+  </si>
+  <si>
+    <t>Machine has coolant/air-blow hardware configured.</t>
+  </si>
+  <si>
+    <t>Material positioned; clamp zone clear.</t>
+  </si>
+  <si>
+    <t>Edge-start/open profile where arc-transfer wait may fail.</t>
+  </si>
+  <si>
+    <t>Cut start/stop point and ignition interlocks are valid.</t>
+  </si>
+  <si>
+    <t>Scribing process selected and scribe hardware installed.</t>
+  </si>
+  <si>
+    <t>Need protected/tool-check torch raise state.</t>
+  </si>
+  <si>
+    <t>Auto-loader/indexer installed and enabled.</t>
+  </si>
+  <si>
+    <t>Machine-specific load routine is configured for this length.</t>
+  </si>
+  <si>
+    <t>Auto-load sensor logic active; material staging expected.</t>
+  </si>
+  <si>
+    <t>Printer head option installed and pressure set.</t>
+  </si>
+  <si>
+    <t>Only in programs that intentionally repurpose M54.</t>
+  </si>
+  <si>
+    <t>Angle-channel center setup completed from main torch.</t>
+  </si>
+  <si>
+    <t>Auto-load lift #1 available and safe to actuate.</t>
+  </si>
+  <si>
+    <t>Auto-load lift #2 available and safe to actuate.</t>
+  </si>
+  <si>
+    <t>Auto-load lift #3 available and safe to actuate.</t>
+  </si>
+  <si>
+    <t>Auto-load lift #4 available and safe to actuate.</t>
+  </si>
+  <si>
+    <t>Pneumatic torch lift configuration (or compatibility call).</t>
+  </si>
+  <si>
+    <t>Machine equipped with lift #5/#6 functions.</t>
+  </si>
+  <si>
+    <t>Primary chuck hardware available and homed.</t>
+  </si>
+  <si>
+    <t>Part sensor/air-blast circuit available.</t>
+  </si>
+  <si>
+    <t>Lift-bank command enabled for all loading lifts.</t>
+  </si>
+  <si>
+    <t>Auto-load cycle context; indexer/lifts/clamp logic valid.</t>
+  </si>
+  <si>
+    <t>Only where site-specific macro defines behavior.</t>
+  </si>
+  <si>
+    <t>Ejector pin option installed and part-handling state valid.</t>
+  </si>
+  <si>
+    <t>Torch-on behavior triggered via M15 compatibility path.</t>
+  </si>
+  <si>
+    <t>Torch-off behavior triggered via M16 compatibility path.</t>
+  </si>
+  <si>
+    <t>Coolant/air-blow state changed per command.</t>
+  </si>
+  <si>
+    <t>Clamp/scriber actuator toggled (machine-dependent).</t>
+  </si>
+  <si>
+    <t>Ignition issued without waiting for transferred arc.</t>
+  </si>
+  <si>
+    <t>Torch state toggled for cut sequence.</t>
+  </si>
+  <si>
+    <t>Scribe extended/retracted and temporary offsets handled.</t>
+  </si>
+  <si>
+    <t>Torch raised to configured G28/tool-check position.</t>
+  </si>
+  <si>
+    <t>Tube loader/indexer cycle fired.</t>
+  </si>
+  <si>
+    <t>Material load/stage macro sequence executed.</t>
+  </si>
+  <si>
+    <t>Material-staged check evaluated; warning/continue path selected.</t>
+  </si>
+  <si>
+    <t>Printer head engaged/disengaged.</t>
+  </si>
+  <si>
+    <t>No standard guaranteed effect; implementation-specific.</t>
+  </si>
+  <si>
+    <t>G55 scribe offset calculated from G54 context.</t>
+  </si>
+  <si>
+    <t>Lift #1 moved up/down.</t>
+  </si>
+  <si>
+    <t>Lift #2 moved up/down.</t>
+  </si>
+  <si>
+    <t>Lift #3 moved up/down.</t>
+  </si>
+  <si>
+    <t>Lift #4 moved up/down.</t>
+  </si>
+  <si>
+    <t>Torch pneumatic lift moved up/down (if present).</t>
+  </si>
+  <si>
+    <t>Lift #5/#6 moved up/down (if equipped).</t>
+  </si>
+  <si>
+    <t>Primary chuck opened/closed.</t>
+  </si>
+  <si>
+    <t>Part-sensor air blast toggled on/off.</t>
+  </si>
+  <si>
+    <t>All loading lifts commanded up/down.</t>
+  </si>
+  <si>
+    <t>Combined auto-load macro actions executed.</t>
+  </si>
+  <si>
+    <t>Machine/site-specific macro action executed.</t>
+  </si>
+  <si>
+    <t>Ejector pin extended/retracted.</t>
+  </si>
+  <si>
+    <t>operator_note</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t>inferred</t>
+  </si>
+  <si>
+    <t>likely</t>
+  </si>
+  <si>
+    <t>confirmed</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>M15</t>
+  </si>
+  <si>
+    <t>M17</t>
+  </si>
+  <si>
+    <t>M46</t>
+  </si>
+  <si>
+    <t>M62</t>
+  </si>
+  <si>
+    <t>M64</t>
+  </si>
+  <si>
+    <t>M66</t>
+  </si>
+  <si>
+    <t>M68</t>
+  </si>
+  <si>
+    <t>M70</t>
+  </si>
+  <si>
+    <t>M72</t>
+  </si>
+  <si>
+    <t>M74</t>
+  </si>
+  <si>
+    <t>M76</t>
+  </si>
+  <si>
+    <t>M78</t>
+  </si>
+  <si>
+    <t>M86</t>
   </si>
 </sst>
 </file>
@@ -275,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -284,6 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -618,13 +871,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1755BD6-0369-4AEA-B900-8D191443ED5C}">
-  <dimension ref="B2:J54"/>
+  <dimension ref="B2:J30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
-    <col min="3" max="3" width="83.5703125" style="1" customWidth="1"/>
-    <col min="4" max="10" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
@@ -656,229 +915,699 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I4" t="s">
+        <v>4</v>
       </c>
       <c r="J4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="60" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I6" t="s">
+        <v>134</v>
       </c>
       <c r="J6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="75" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I9" t="s">
+        <v>136</v>
+      </c>
+      <c r="J9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="75" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" ht="120" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" t="s">
+        <v>131</v>
+      </c>
+      <c r="I10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" t="s">
+        <v>131</v>
+      </c>
+      <c r="I11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="60" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" ht="60" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" t="s">
+        <v>131</v>
+      </c>
+      <c r="I12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" t="s">
+        <v>127</v>
+      </c>
+      <c r="H13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="105" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H14" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="60" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="60" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" t="s">
+        <v>131</v>
+      </c>
+      <c r="I16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" t="s">
+        <v>131</v>
+      </c>
+      <c r="I17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" t="s">
+        <v>131</v>
+      </c>
+      <c r="I18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" ht="45" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="D20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" t="s">
+        <v>127</v>
+      </c>
+      <c r="H20" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="60" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" t="s">
+        <v>131</v>
+      </c>
+      <c r="I22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" t="s">
+        <v>132</v>
+      </c>
+      <c r="I23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" ht="90" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" t="s">
+        <v>132</v>
+      </c>
+      <c r="I24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" t="s">
+        <v>127</v>
+      </c>
+      <c r="H25" t="s">
+        <v>131</v>
+      </c>
+      <c r="I25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="D26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" t="s">
+        <v>131</v>
+      </c>
+      <c r="I26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>29</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>30</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>33</v>
-      </c>
-      <c r="C54" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="D28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" t="s">
+        <v>127</v>
+      </c>
+      <c r="H28" t="s">
+        <v>131</v>
+      </c>
+      <c r="I28" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C30" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
